--- a/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen problemas de riñón</t>
+          <t>Menores que padecen problemas de riñón (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,46</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,22</t>
+          <t>0,48; 5,42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,12</t>
+          <t>0,26; 2,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,07; 0,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,53</t>
+          <t>0,09; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,54</t>
+          <t>0,08; 0,55</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen problemas de riñón (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2309</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3870</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5347</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>589; 6609</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3244</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2648</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2648</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3609</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4909</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>679; 5679</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3281</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2969</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3537</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3418</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4734</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>582; 5424</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>523; 5458</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 5501</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1241; 7242</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1178; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,42</t>
+          <t>0,48; 5,12</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,15</t>
+          <t>0,26; 2,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,76</t>
+          <t>0,07; 0,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,52</t>
+          <t>0,09; 0,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,55</t>
+          <t>0,08; 0,57</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3870</t>
+          <t>0; 3687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5347</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>589; 6609</t>
+          <t>588; 6243</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3376</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 3605</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>0; 3692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>0; 2870</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4909</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>679; 5679</t>
+          <t>678; 6278</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2969</t>
+          <t>0; 2965</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3918</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 2946</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4734</t>
+          <t>0; 4837</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>582; 5424</t>
+          <t>583; 5521</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>523; 5458</t>
+          <t>523; 4896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1241; 7242</t>
+          <t>1200; 7576</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1178; 7953</t>
+          <t>1193; 8226</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2,13%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 7,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,12</t>
+          <t>0,48; 5,22</t>
         </is>
       </c>
     </row>
@@ -745,22 +745,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,38</t>
+          <t>0,26; 2,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1395,24 +1395,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1568,27 +1568,27 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,86</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,72</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>0,08; 0,78</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,68</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,75</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,54</t>
+          <t>0,05; 0,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,57</t>
+          <t>0,08; 0,54</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1765,22 +1765,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1818,22 +1818,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>1221</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 4922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5289</t>
+          <t>0; 4283</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>588; 6243</t>
+          <t>580; 6357</t>
         </is>
       </c>
     </row>
@@ -1928,22 +1928,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1981,22 +1981,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>604</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3577</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3605</t>
+          <t>0; 3022</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2646</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3692</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>0; 2622</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2733,22 +2733,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>720</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3606</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 4085</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>678; 6278</t>
+          <t>679; 5596</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2896,22 +2896,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,24 +2949,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3265</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2965</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3918</t>
+          <t>0; 3929</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2946</t>
+          <t>0; 3217</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1824</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4837</t>
+          <t>525; 5757</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>583; 5521</t>
+          <t>0; 6377</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>523; 4896</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 5588</t>
+          <t>582; 5523</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1200; 7576</t>
+          <t>721; 7477</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1193; 8226</t>
+          <t>1224; 7871</t>
         </is>
       </c>
     </row>
